--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/monthly/2026년 2월 월별 발주 예측.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/monthly/2026년 2월 월별 발주 예측.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>예측</t>
+          <t>납기</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
